--- a/Mars_Rover/Mars_Rover_BOM.xlsx
+++ b/Mars_Rover/Mars_Rover_BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\_WNCC\GitHub\WNCCNASA\Mars_Rover\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\_WNCC\NASA_Fellowship\Mars_Rover\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AD54F2-0A3B-446F-BA24-866750C7DAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1733E8-E41C-44D7-8FFF-9CF67EC744DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34590" yWindow="2940" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>motors 6v 130rpm</t>
-  </si>
-  <si>
     <t>https://www.aliexpress.us/item/2255801128158539.html?spm=a2g0o.order_list.order_list_main.5.5a041802HcKiys&amp;gatewayAdapt=glo2usa</t>
   </si>
   <si>
@@ -153,6 +150,9 @@
   </si>
   <si>
     <t>Jumper kit</t>
+  </si>
+  <si>
+    <t>JGA25-370 motors 6v 130rpm</t>
   </si>
 </sst>
 </file>
@@ -535,7 +535,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -551,7 +551,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C3" s="5">
         <v>8.91</v>
@@ -561,7 +561,7 @@
         <v>53.46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -569,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5">
         <v>8.6</v>
@@ -579,7 +579,7 @@
         <v>51.599999999999994</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -587,7 +587,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5">
         <v>14.32</v>
@@ -597,7 +597,7 @@
         <v>28.64</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -605,7 +605,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="5">
         <v>22.99</v>
@@ -615,7 +615,7 @@
         <v>22.99</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="5">
         <v>26.99</v>
@@ -633,7 +633,7 @@
         <v>26.99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5">
         <v>9.49</v>
@@ -651,7 +651,7 @@
         <v>9.49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -659,7 +659,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5">
         <v>7.99</v>
@@ -669,7 +669,7 @@
         <v>15.98</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -677,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5">
         <v>12.99</v>
@@ -687,7 +687,7 @@
         <v>12.99</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -695,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="5">
         <v>18.989999999999998</v>
@@ -705,7 +705,7 @@
         <v>18.989999999999998</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="5">
         <v>12.99</v>
@@ -723,7 +723,7 @@
         <v>12.99</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -731,7 +731,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="5">
         <v>9.25</v>
@@ -741,7 +741,7 @@
         <v>9.25</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -749,7 +749,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="5">
         <v>19.989999999999998</v>
@@ -759,7 +759,7 @@
         <v>19.989999999999998</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="5">
         <v>30.59</v>
@@ -777,7 +777,7 @@
         <v>30.59</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -785,7 +785,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="5">
         <v>45.89</v>
@@ -795,7 +795,7 @@
         <v>45.89</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -803,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="5">
         <v>7.99</v>
@@ -813,7 +813,7 @@
         <v>7.99</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="5">
         <v>9.99</v>
@@ -831,7 +831,7 @@
         <v>9.99</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="5">
         <v>13.49</v>
@@ -849,7 +849,7 @@
         <v>13.49</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -857,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="5">
         <v>25</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
